--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -87472,13 +87472,13 @@
         <v>2.63</v>
       </c>
       <c r="AU399" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV399" t="n">
         <v>4</v>
       </c>
       <c r="AW399" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AX399" t="n">
         <v>7</v>
@@ -87911,13 +87911,13 @@
         <v>1</v>
       </c>
       <c r="AV401" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW401" t="n">
         <v>9</v>
       </c>
       <c r="AX401" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY401" t="n">
         <v>10</v>
@@ -88132,13 +88132,13 @@
         <v>4</v>
       </c>
       <c r="AW402" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX402" t="n">
         <v>8</v>
       </c>
       <c r="AY402" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ402" t="n">
         <v>12</v>
@@ -88350,13 +88350,13 @@
         <v>0</v>
       </c>
       <c r="AW403" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX403" t="n">
         <v>5</v>
       </c>
       <c r="AY403" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ403" t="n">
         <v>5</v>

--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -87475,7 +87475,7 @@
         <v>6</v>
       </c>
       <c r="AV399" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW399" t="n">
         <v>10</v>
@@ -87487,7 +87487,7 @@
         <v>16</v>
       </c>
       <c r="AZ399" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA399" t="n">
         <v>13</v>

--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -87690,7 +87690,7 @@
         <v>2.98</v>
       </c>
       <c r="AU400" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV400" t="n">
         <v>4</v>
@@ -87702,7 +87702,7 @@
         <v>8</v>
       </c>
       <c r="AY400" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ400" t="n">
         <v>12</v>
@@ -88132,13 +88132,13 @@
         <v>4</v>
       </c>
       <c r="AW402" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX402" t="n">
         <v>8</v>
       </c>
       <c r="AY402" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ402" t="n">
         <v>12</v>
@@ -88350,16 +88350,16 @@
         <v>0</v>
       </c>
       <c r="AW403" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX403" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY403" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ403" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA403" t="n">
         <v>8</v>
@@ -88565,13 +88565,13 @@
         <v>5</v>
       </c>
       <c r="AV404" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AW404" t="n">
         <v>12</v>
       </c>
       <c r="AX404" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY404" t="n">
         <v>17</v>
@@ -89216,19 +89216,19 @@
         <v>2.91</v>
       </c>
       <c r="AU407" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AV407" t="n">
         <v>2</v>
       </c>
       <c r="AW407" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX407" t="n">
         <v>6</v>
       </c>
       <c r="AY407" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ407" t="n">
         <v>8</v>

--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP407"/>
+  <dimension ref="A1:BP412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.88</v>
@@ -1350,7 +1350,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ8" t="n">
         <v>1.65</v>
@@ -2440,7 +2440,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR9" t="n">
         <v>0</v>
@@ -3091,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ12" t="n">
         <v>0.5600000000000001</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ13" t="n">
         <v>1.56</v>
@@ -3530,7 +3530,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3963,7 +3963,7 @@
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ16" t="n">
         <v>1.59</v>
@@ -4620,7 +4620,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -6361,7 +6361,7 @@
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ27" t="n">
         <v>0.71</v>
@@ -6797,10 +6797,10 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR29" t="n">
         <v>1.09</v>
@@ -7015,7 +7015,7 @@
         <v>3</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.83</v>
@@ -8326,7 +8326,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR36" t="n">
         <v>0.89</v>
@@ -8759,10 +8759,10 @@
         <v>3</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ38" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR38" t="n">
         <v>0.62</v>
@@ -10506,7 +10506,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR46" t="n">
         <v>1.66</v>
@@ -10721,7 +10721,7 @@
         <v>1</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ47" t="n">
         <v>1.59</v>
@@ -11157,7 +11157,7 @@
         <v>2</v>
       </c>
       <c r="AP49" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ49" t="n">
         <v>1.76</v>
@@ -11375,10 +11375,10 @@
         <v>3</v>
       </c>
       <c r="AP50" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR50" t="n">
         <v>1.11</v>
@@ -12904,7 +12904,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ57" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR57" t="n">
         <v>1.05</v>
@@ -13122,7 +13122,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR58" t="n">
         <v>1.68</v>
@@ -14212,7 +14212,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ63" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR63" t="n">
         <v>1.18</v>
@@ -14427,7 +14427,7 @@
         <v>0</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ64" t="n">
         <v>0.71</v>
@@ -15299,7 +15299,7 @@
         <v>2</v>
       </c>
       <c r="AP68" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.88</v>
@@ -15953,7 +15953,7 @@
         <v>0</v>
       </c>
       <c r="AP71" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ71" t="n">
         <v>0.5600000000000001</v>
@@ -16174,7 +16174,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ72" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR72" t="n">
         <v>1.75</v>
@@ -16389,7 +16389,7 @@
         <v>1</v>
       </c>
       <c r="AP73" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.71</v>
@@ -16828,7 +16828,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR75" t="n">
         <v>1.56</v>
@@ -17918,7 +17918,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR80" t="n">
         <v>1.77</v>
@@ -18136,7 +18136,7 @@
         <v>2</v>
       </c>
       <c r="AQ81" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR81" t="n">
         <v>1.18</v>
@@ -18351,7 +18351,7 @@
         <v>2</v>
       </c>
       <c r="AP82" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ82" t="n">
         <v>1.39</v>
@@ -18787,7 +18787,7 @@
         <v>1.67</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ84" t="n">
         <v>1.18</v>
@@ -19008,7 +19008,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR85" t="n">
         <v>1.21</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ90" t="n">
         <v>1.53</v>
@@ -20749,7 +20749,7 @@
         <v>2.33</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ93" t="n">
         <v>1.76</v>
@@ -21406,7 +21406,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR96" t="n">
         <v>1.23</v>
@@ -21842,7 +21842,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ98" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR98" t="n">
         <v>1.57</v>
@@ -22929,7 +22929,7 @@
         <v>1.5</v>
       </c>
       <c r="AP103" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ103" t="n">
         <v>1.18</v>
@@ -23147,7 +23147,7 @@
         <v>1.5</v>
       </c>
       <c r="AP104" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ104" t="n">
         <v>1.39</v>
@@ -23365,10 +23365,10 @@
         <v>1.33</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR105" t="n">
         <v>1.23</v>
@@ -23804,7 +23804,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR107" t="n">
         <v>1.22</v>
@@ -24894,7 +24894,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR112" t="n">
         <v>1.08</v>
@@ -25327,7 +25327,7 @@
         <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.83</v>
@@ -25545,7 +25545,7 @@
         <v>0.25</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.82</v>
@@ -26420,7 +26420,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR119" t="n">
         <v>1.43</v>
@@ -27071,7 +27071,7 @@
         <v>1.8</v>
       </c>
       <c r="AP122" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ122" t="n">
         <v>1.65</v>
@@ -27728,7 +27728,7 @@
         <v>2</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR125" t="n">
         <v>1.35</v>
@@ -28161,7 +28161,7 @@
         <v>1.4</v>
       </c>
       <c r="AP127" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ127" t="n">
         <v>0.71</v>
@@ -28815,10 +28815,10 @@
         <v>1</v>
       </c>
       <c r="AP130" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ130" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR130" t="n">
         <v>1.73</v>
@@ -29036,7 +29036,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR131" t="n">
         <v>1.17</v>
@@ -29469,10 +29469,10 @@
         <v>1</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ133" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR133" t="n">
         <v>2.04</v>
@@ -29905,10 +29905,10 @@
         <v>1.8</v>
       </c>
       <c r="AP135" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ135" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR135" t="n">
         <v>1.53</v>
@@ -31870,7 +31870,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ144" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR144" t="n">
         <v>1.9</v>
@@ -32521,10 +32521,10 @@
         <v>1.17</v>
       </c>
       <c r="AP147" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ147" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR147" t="n">
         <v>1.5</v>
@@ -32739,7 +32739,7 @@
         <v>1.5</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ148" t="n">
         <v>1.18</v>
@@ -33611,7 +33611,7 @@
         <v>0.33</v>
       </c>
       <c r="AP152" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ152" t="n">
         <v>0.82</v>
@@ -34047,7 +34047,7 @@
         <v>1.17</v>
       </c>
       <c r="AP154" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ154" t="n">
         <v>0.88</v>
@@ -34268,7 +34268,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR155" t="n">
         <v>1.24</v>
@@ -35794,7 +35794,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR162" t="n">
         <v>1.45</v>
@@ -36448,7 +36448,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ165" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR165" t="n">
         <v>1.81</v>
@@ -37099,7 +37099,7 @@
         <v>2.33</v>
       </c>
       <c r="AP168" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ168" t="n">
         <v>1.76</v>
@@ -37320,7 +37320,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ169" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR169" t="n">
         <v>1.64</v>
@@ -37971,7 +37971,7 @@
         <v>0.57</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ172" t="n">
         <v>1.12</v>
@@ -38628,7 +38628,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR175" t="n">
         <v>1.85</v>
@@ -39064,7 +39064,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ177" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR177" t="n">
         <v>1.37</v>
@@ -39282,7 +39282,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ178" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR178" t="n">
         <v>1.52</v>
@@ -39497,7 +39497,7 @@
         <v>1.57</v>
       </c>
       <c r="AP179" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ179" t="n">
         <v>1.71</v>
@@ -40369,10 +40369,10 @@
         <v>1.29</v>
       </c>
       <c r="AP183" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR183" t="n">
         <v>1.48</v>
@@ -40587,7 +40587,7 @@
         <v>1.43</v>
       </c>
       <c r="AP184" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ184" t="n">
         <v>0.88</v>
@@ -40808,7 +40808,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ185" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR185" t="n">
         <v>1.27</v>
@@ -41677,7 +41677,7 @@
         <v>1.14</v>
       </c>
       <c r="AP189" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ189" t="n">
         <v>1.39</v>
@@ -43206,7 +43206,7 @@
         <v>2</v>
       </c>
       <c r="AQ196" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR196" t="n">
         <v>1.42</v>
@@ -44293,10 +44293,10 @@
         <v>1.5</v>
       </c>
       <c r="AP201" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR201" t="n">
         <v>1.73</v>
@@ -45383,10 +45383,10 @@
         <v>1.13</v>
       </c>
       <c r="AP206" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ206" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR206" t="n">
         <v>1.93</v>
@@ -45604,7 +45604,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR207" t="n">
         <v>1.54</v>
@@ -45822,7 +45822,7 @@
         <v>1.88</v>
       </c>
       <c r="AQ208" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR208" t="n">
         <v>1.22</v>
@@ -46473,7 +46473,7 @@
         <v>1.63</v>
       </c>
       <c r="AP211" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ211" t="n">
         <v>1.65</v>
@@ -47127,7 +47127,7 @@
         <v>1.25</v>
       </c>
       <c r="AP214" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ214" t="n">
         <v>0.88</v>
@@ -47563,7 +47563,7 @@
         <v>1.38</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.82</v>
@@ -49089,7 +49089,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP223" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ223" t="n">
         <v>0.5600000000000001</v>
@@ -49528,7 +49528,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ225" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR225" t="n">
         <v>1.39</v>
@@ -49964,7 +49964,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ227" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR227" t="n">
         <v>1.1</v>
@@ -50836,7 +50836,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ231" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR231" t="n">
         <v>1.91</v>
@@ -51487,7 +51487,7 @@
         <v>1.78</v>
       </c>
       <c r="AP234" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ234" t="n">
         <v>1.59</v>
@@ -52359,7 +52359,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP238" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ238" t="n">
         <v>0.71</v>
@@ -52580,7 +52580,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ239" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR239" t="n">
         <v>1.84</v>
@@ -52795,10 +52795,10 @@
         <v>0.89</v>
       </c>
       <c r="AP240" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ240" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR240" t="n">
         <v>1.16</v>
@@ -53013,7 +53013,7 @@
         <v>1.56</v>
       </c>
       <c r="AP241" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ241" t="n">
         <v>1.56</v>
@@ -54103,7 +54103,7 @@
         <v>1.4</v>
       </c>
       <c r="AP246" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ246" t="n">
         <v>1.59</v>
@@ -54760,7 +54760,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ249" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR249" t="n">
         <v>1.7</v>
@@ -55632,7 +55632,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ253" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR253" t="n">
         <v>1.88</v>
@@ -56504,7 +56504,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ257" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR257" t="n">
         <v>1.84</v>
@@ -56719,7 +56719,7 @@
         <v>1.7</v>
       </c>
       <c r="AP258" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ258" t="n">
         <v>1.56</v>
@@ -56937,7 +56937,7 @@
         <v>1.4</v>
       </c>
       <c r="AP259" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ259" t="n">
         <v>1.29</v>
@@ -57155,7 +57155,7 @@
         <v>1.6</v>
       </c>
       <c r="AP260" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ260" t="n">
         <v>1.59</v>
@@ -57373,10 +57373,10 @@
         <v>1.3</v>
       </c>
       <c r="AP261" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ261" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR261" t="n">
         <v>1.89</v>
@@ -58248,7 +58248,7 @@
         <v>1</v>
       </c>
       <c r="AQ265" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR265" t="n">
         <v>1.36</v>
@@ -58463,7 +58463,7 @@
         <v>1.27</v>
       </c>
       <c r="AP266" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ266" t="n">
         <v>1.29</v>
@@ -58681,7 +58681,7 @@
         <v>1</v>
       </c>
       <c r="AP267" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ267" t="n">
         <v>1.53</v>
@@ -58899,7 +58899,7 @@
         <v>0.55</v>
       </c>
       <c r="AP268" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ268" t="n">
         <v>0.71</v>
@@ -59117,10 +59117,10 @@
         <v>1.27</v>
       </c>
       <c r="AP269" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ269" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR269" t="n">
         <v>1.47</v>
@@ -59338,7 +59338,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ270" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR270" t="n">
         <v>1.99</v>
@@ -60428,7 +60428,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ275" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR275" t="n">
         <v>1.78</v>
@@ -61300,7 +61300,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ279" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR279" t="n">
         <v>1.22</v>
@@ -61736,7 +61736,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ281" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR281" t="n">
         <v>1.3</v>
@@ -61951,7 +61951,7 @@
         <v>1</v>
       </c>
       <c r="AP282" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ282" t="n">
         <v>0.83</v>
@@ -64785,7 +64785,7 @@
         <v>1.77</v>
       </c>
       <c r="AP295" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ295" t="n">
         <v>1.82</v>
@@ -65442,7 +65442,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ298" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR298" t="n">
         <v>1.34</v>
@@ -66096,7 +66096,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ301" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR301" t="n">
         <v>1.34</v>
@@ -66747,7 +66747,7 @@
         <v>1.67</v>
       </c>
       <c r="AP304" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ304" t="n">
         <v>1.59</v>
@@ -67404,7 +67404,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ307" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR307" t="n">
         <v>1.92</v>
@@ -67840,7 +67840,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ309" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR309" t="n">
         <v>1.51</v>
@@ -68491,7 +68491,7 @@
         <v>1.83</v>
       </c>
       <c r="AP312" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ312" t="n">
         <v>1.65</v>
@@ -69145,7 +69145,7 @@
         <v>1</v>
       </c>
       <c r="AP315" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ315" t="n">
         <v>1.12</v>
@@ -69363,7 +69363,7 @@
         <v>1.38</v>
       </c>
       <c r="AP316" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ316" t="n">
         <v>1.39</v>
@@ -69584,7 +69584,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ317" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR317" t="n">
         <v>1.6</v>
@@ -69799,7 +69799,7 @@
         <v>1</v>
       </c>
       <c r="AP318" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ318" t="n">
         <v>1.12</v>
@@ -70017,7 +70017,7 @@
         <v>1.08</v>
       </c>
       <c r="AP319" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ319" t="n">
         <v>1.29</v>
@@ -70671,7 +70671,7 @@
         <v>0.57</v>
       </c>
       <c r="AP322" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ322" t="n">
         <v>0.5600000000000001</v>
@@ -70892,7 +70892,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ323" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR323" t="n">
         <v>1.35</v>
@@ -71764,7 +71764,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ327" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR327" t="n">
         <v>1.84</v>
@@ -72197,7 +72197,7 @@
         <v>1.69</v>
       </c>
       <c r="AP329" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ329" t="n">
         <v>1.76</v>
@@ -72851,7 +72851,7 @@
         <v>1.85</v>
       </c>
       <c r="AP332" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ332" t="n">
         <v>1.71</v>
@@ -73726,7 +73726,7 @@
         <v>1</v>
       </c>
       <c r="AQ336" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR336" t="n">
         <v>1.5</v>
@@ -74162,7 +74162,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ338" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR338" t="n">
         <v>1.52</v>
@@ -75470,7 +75470,7 @@
         <v>1.59</v>
       </c>
       <c r="AQ344" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR344" t="n">
         <v>1.61</v>
@@ -75688,7 +75688,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ345" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR345" t="n">
         <v>1.39</v>
@@ -76560,7 +76560,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ349" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR349" t="n">
         <v>1.85</v>
@@ -76775,7 +76775,7 @@
         <v>1.5</v>
       </c>
       <c r="AP350" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ350" t="n">
         <v>1.59</v>
@@ -77865,7 +77865,7 @@
         <v>1.64</v>
       </c>
       <c r="AP355" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ355" t="n">
         <v>1.59</v>
@@ -78519,7 +78519,7 @@
         <v>1.14</v>
       </c>
       <c r="AP358" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ358" t="n">
         <v>1.12</v>
@@ -79176,7 +79176,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ361" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR361" t="n">
         <v>1.22</v>
@@ -79391,7 +79391,7 @@
         <v>0.73</v>
       </c>
       <c r="AP362" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ362" t="n">
         <v>0.88</v>
@@ -79830,7 +79830,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ364" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR364" t="n">
         <v>1.56</v>
@@ -80699,7 +80699,7 @@
         <v>1.71</v>
       </c>
       <c r="AP368" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ368" t="n">
         <v>1.56</v>
@@ -81353,7 +81353,7 @@
         <v>1.13</v>
       </c>
       <c r="AP371" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AQ371" t="n">
         <v>1.18</v>
@@ -82010,7 +82010,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ374" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AR374" t="n">
         <v>1.42</v>
@@ -82882,7 +82882,7 @@
         <v>2.24</v>
       </c>
       <c r="AQ378" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AR378" t="n">
         <v>1.52</v>
@@ -83315,7 +83315,7 @@
         <v>0.8</v>
       </c>
       <c r="AP380" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ380" t="n">
         <v>0.82</v>
@@ -83533,7 +83533,7 @@
         <v>1.67</v>
       </c>
       <c r="AP381" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="AQ381" t="n">
         <v>1.71</v>
@@ -84187,7 +84187,7 @@
         <v>1.44</v>
       </c>
       <c r="AP384" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="AQ384" t="n">
         <v>1.53</v>
@@ -85062,7 +85062,7 @@
         <v>2</v>
       </c>
       <c r="AQ388" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR388" t="n">
         <v>1.45</v>
@@ -85498,7 +85498,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ390" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR390" t="n">
         <v>1.16</v>
@@ -85934,7 +85934,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ392" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AR392" t="n">
         <v>1.82</v>
@@ -86149,7 +86149,7 @@
         <v>1.73</v>
       </c>
       <c r="AP393" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AQ393" t="n">
         <v>1.76</v>
@@ -87675,7 +87675,7 @@
         <v>1.19</v>
       </c>
       <c r="AP400" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="AQ400" t="n">
         <v>1.12</v>
@@ -88550,7 +88550,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ404" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AR404" t="n">
         <v>1.4</v>
@@ -88986,7 +88986,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ406" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AR406" t="n">
         <v>1.6</v>
@@ -89280,6 +89280,1096 @@
       </c>
       <c r="BP407" t="n">
         <v>1.33</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="1" t="n">
+        <v>407</v>
+      </c>
+      <c r="B408" t="n">
+        <v>8217390</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F408" t="n">
+        <v>25</v>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>Walsall</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Fleetwood Town</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>0</v>
+      </c>
+      <c r="J408" t="n">
+        <v>1</v>
+      </c>
+      <c r="K408" t="n">
+        <v>1</v>
+      </c>
+      <c r="L408" t="n">
+        <v>0</v>
+      </c>
+      <c r="M408" t="n">
+        <v>1</v>
+      </c>
+      <c r="N408" t="n">
+        <v>1</v>
+      </c>
+      <c r="O408" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P408" t="inlineStr">
+        <is>
+          <t>['15']</t>
+        </is>
+      </c>
+      <c r="Q408" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R408" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S408" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T408" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U408" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V408" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="W408" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X408" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="Y408" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z408" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA408" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB408" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AC408" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD408" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AE408" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AF408" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AG408" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AH408" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AI408" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AJ408" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AK408" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL408" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM408" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN408" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AO408" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AP408" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ408" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AR408" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AS408" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT408" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="AU408" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV408" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW408" t="n">
+        <v>14</v>
+      </c>
+      <c r="AX408" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY408" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ408" t="n">
+        <v>6</v>
+      </c>
+      <c r="BA408" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB408" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC408" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD408" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BE408" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="BF408" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG408" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH408" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="BI408" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BJ408" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BK408" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BL408" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BM408" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BN408" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="BO408" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BP408" t="n">
+        <v>1.29</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="1" t="n">
+        <v>408</v>
+      </c>
+      <c r="B409" t="n">
+        <v>8217645</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F409" t="n">
+        <v>25</v>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>Newport County</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>1</v>
+      </c>
+      <c r="J409" t="n">
+        <v>1</v>
+      </c>
+      <c r="K409" t="n">
+        <v>2</v>
+      </c>
+      <c r="L409" t="n">
+        <v>3</v>
+      </c>
+      <c r="M409" t="n">
+        <v>1</v>
+      </c>
+      <c r="N409" t="n">
+        <v>4</v>
+      </c>
+      <c r="O409" t="inlineStr">
+        <is>
+          <t>['35', '88', '90+6']</t>
+        </is>
+      </c>
+      <c r="P409" t="inlineStr">
+        <is>
+          <t>['2']</t>
+        </is>
+      </c>
+      <c r="Q409" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="R409" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="S409" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T409" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U409" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="V409" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="W409" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X409" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="Y409" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z409" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA409" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AB409" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC409" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD409" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AE409" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF409" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AG409" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AH409" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AI409" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ409" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AK409" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AL409" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AM409" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AN409" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AO409" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AP409" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="AQ409" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR409" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AS409" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT409" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AU409" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV409" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW409" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX409" t="n">
+        <v>4</v>
+      </c>
+      <c r="AY409" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ409" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA409" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB409" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC409" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD409" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BE409" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="BF409" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BG409" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BH409" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BI409" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ409" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="BK409" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL409" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BM409" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="BN409" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BO409" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="BP409" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="1" t="n">
+        <v>409</v>
+      </c>
+      <c r="B410" t="n">
+        <v>8217569</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F410" t="n">
+        <v>25</v>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>Bromley</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Oldham Athletic</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>0</v>
+      </c>
+      <c r="J410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L410" t="n">
+        <v>0</v>
+      </c>
+      <c r="M410" t="n">
+        <v>0</v>
+      </c>
+      <c r="N410" t="n">
+        <v>0</v>
+      </c>
+      <c r="O410" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P410" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q410" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="R410" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S410" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="T410" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U410" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="V410" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="W410" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X410" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="Y410" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z410" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA410" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB410" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC410" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD410" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE410" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AF410" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AG410" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AH410" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AI410" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AJ410" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AK410" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL410" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AM410" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN410" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO410" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AP410" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AQ410" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AR410" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AS410" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AT410" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU410" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV410" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW410" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX410" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY410" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ410" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA410" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB410" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC410" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD410" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BE410" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="BF410" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="BG410" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH410" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="BI410" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ410" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BK410" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL410" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM410" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BN410" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO410" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BP410" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="B411" t="n">
+        <v>8217462</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F411" t="n">
+        <v>26</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>Grimsby Town</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Salford City</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>3</v>
+      </c>
+      <c r="J411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K411" t="n">
+        <v>3</v>
+      </c>
+      <c r="L411" t="n">
+        <v>3</v>
+      </c>
+      <c r="M411" t="n">
+        <v>1</v>
+      </c>
+      <c r="N411" t="n">
+        <v>4</v>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>['33', '39', '42']</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>['53']</t>
+        </is>
+      </c>
+      <c r="Q411" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="R411" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="S411" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="T411" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U411" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="V411" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="W411" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="X411" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="Y411" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Z411" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA411" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AB411" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AC411" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD411" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE411" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AF411" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AG411" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AH411" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AI411" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ411" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AK411" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AL411" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM411" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AN411" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO411" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AP411" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AQ411" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AR411" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AS411" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AT411" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="AU411" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV411" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW411" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX411" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY411" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ411" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA411" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB411" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC411" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD411" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BE411" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BF411" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BG411" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BH411" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI411" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BJ411" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BK411" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BL411" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="BM411" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN411" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BO411" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BP411" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="1" t="n">
+        <v>411</v>
+      </c>
+      <c r="B412" t="n">
+        <v>8217391</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>England EFL League Two</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="n">
+        <v>46084.69791666666</v>
+      </c>
+      <c r="F412" t="n">
+        <v>26</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Colchester United</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>2</v>
+      </c>
+      <c r="J412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K412" t="n">
+        <v>2</v>
+      </c>
+      <c r="L412" t="n">
+        <v>3</v>
+      </c>
+      <c r="M412" t="n">
+        <v>0</v>
+      </c>
+      <c r="N412" t="n">
+        <v>3</v>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>['26', '39', '72']</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q412" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="R412" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="S412" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T412" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="U412" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="V412" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="W412" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X412" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Y412" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z412" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA412" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB412" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC412" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD412" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE412" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AF412" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AG412" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH412" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AI412" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ412" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK412" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AL412" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM412" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AN412" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AO412" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AP412" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AQ412" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AR412" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS412" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AT412" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AU412" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV412" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW412" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX412" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY412" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ412" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA412" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB412" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC412" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD412" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="BE412" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BF412" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG412" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH412" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BI412" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BJ412" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BK412" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BL412" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BM412" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BN412" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BO412" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BP412" t="n">
+        <v>1.36</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -89870,13 +89870,13 @@
         <v>3.25</v>
       </c>
       <c r="AU410" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV410" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW410" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX410" t="n">
         <v>6</v>
@@ -89885,7 +89885,7 @@
         <v>14</v>
       </c>
       <c r="AZ410" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA410" t="n">
         <v>3</v>

--- a/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/England EFL League Two_20252026.xlsx
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ11" t="n">
         <v>1.18</v>
@@ -5928,7 +5928,7 @@
         <v>1.89</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR25" t="n">
         <v>0</v>
@@ -9852,7 +9852,7 @@
         <v>1.65</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR43" t="n">
         <v>1.11</v>
@@ -12686,7 +12686,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR56" t="n">
         <v>1.64</v>
@@ -13337,7 +13337,7 @@
         <v>2</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ59" t="n">
         <v>1.59</v>
@@ -19005,7 +19005,7 @@
         <v>1.67</v>
       </c>
       <c r="AP85" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ85" t="n">
         <v>1.33</v>
@@ -20098,7 +20098,7 @@
         <v>1.61</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR90" t="n">
         <v>1.92</v>
@@ -25112,7 +25112,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AQ113" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR113" t="n">
         <v>1.51</v>
@@ -26199,7 +26199,7 @@
         <v>1.75</v>
       </c>
       <c r="AP118" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ118" t="n">
         <v>1.71</v>
@@ -30126,7 +30126,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ136" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR136" t="n">
         <v>1.34</v>
@@ -30995,7 +30995,7 @@
         <v>0.8</v>
       </c>
       <c r="AP140" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ140" t="n">
         <v>0.83</v>
@@ -33829,7 +33829,7 @@
         <v>2</v>
       </c>
       <c r="AP153" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ153" t="n">
         <v>1.61</v>
@@ -35576,7 +35576,7 @@
         <v>2</v>
       </c>
       <c r="AQ161" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR161" t="n">
         <v>1.49</v>
@@ -37317,7 +37317,7 @@
         <v>1.33</v>
       </c>
       <c r="AP169" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ169" t="n">
         <v>1</v>
@@ -39718,7 +39718,7 @@
         <v>1.76</v>
       </c>
       <c r="AQ180" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR180" t="n">
         <v>2.04</v>
@@ -40151,7 +40151,7 @@
         <v>1</v>
       </c>
       <c r="AP182" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ182" t="n">
         <v>0.71</v>
@@ -45168,7 +45168,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR205" t="n">
         <v>1.08</v>
@@ -45601,7 +45601,7 @@
         <v>1.5</v>
       </c>
       <c r="AP207" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ207" t="n">
         <v>1.41</v>
@@ -51269,7 +51269,7 @@
         <v>1.22</v>
       </c>
       <c r="AP233" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ233" t="n">
         <v>1.78</v>
@@ -51926,7 +51926,7 @@
         <v>1.94</v>
       </c>
       <c r="AQ236" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR236" t="n">
         <v>1.3</v>
@@ -55847,7 +55847,7 @@
         <v>1.2</v>
       </c>
       <c r="AP254" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ254" t="n">
         <v>0.89</v>
@@ -56068,7 +56068,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ255" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR255" t="n">
         <v>1.77</v>
@@ -58684,7 +58684,7 @@
         <v>1.72</v>
       </c>
       <c r="AQ267" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR267" t="n">
         <v>1.54</v>
@@ -60207,7 +60207,7 @@
         <v>0.91</v>
       </c>
       <c r="AP274" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ274" t="n">
         <v>0.83</v>
@@ -65003,7 +65003,7 @@
         <v>1.58</v>
       </c>
       <c r="AP296" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ296" t="n">
         <v>1.76</v>
@@ -65878,7 +65878,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ300" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR300" t="n">
         <v>1.33</v>
@@ -73287,7 +73287,7 @@
         <v>0.85</v>
       </c>
       <c r="AP334" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ334" t="n">
         <v>0.82</v>
@@ -73508,7 +73508,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ335" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR335" t="n">
         <v>1.63</v>
@@ -75467,7 +75467,7 @@
         <v>1.79</v>
       </c>
       <c r="AP344" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ344" t="n">
         <v>1.56</v>
@@ -77432,7 +77432,7 @@
         <v>0.67</v>
       </c>
       <c r="AQ353" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR353" t="n">
         <v>1.41</v>
@@ -78086,7 +78086,7 @@
         <v>1.06</v>
       </c>
       <c r="AQ356" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR356" t="n">
         <v>1.61</v>
@@ -84190,7 +84190,7 @@
         <v>0.72</v>
       </c>
       <c r="AQ384" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="AR384" t="n">
         <v>1.24</v>
@@ -84623,7 +84623,7 @@
         <v>0.4</v>
       </c>
       <c r="AP386" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ386" t="n">
         <v>0.83</v>
@@ -86367,7 +86367,7 @@
         <v>1.5</v>
       </c>
       <c r="AP394" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AQ394" t="n">
         <v>1.5</v>
@@ -90742,7 +90742,7 @@
         <v>3.2</v>
       </c>
       <c r="AU414" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV414" t="n">
         <v>5</v>
@@ -90754,7 +90754,7 @@
         <v>2</v>
       </c>
       <c r="AY414" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ414" t="n">
         <v>7</v>
@@ -91187,13 +91187,13 @@
         <v>9</v>
       </c>
       <c r="AX416" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY416" t="n">
         <v>12</v>
       </c>
       <c r="AZ416" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA416" t="n">
         <v>8</v>
@@ -91405,13 +91405,13 @@
         <v>10</v>
       </c>
       <c r="AX417" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY417" t="n">
         <v>18</v>
       </c>
       <c r="AZ417" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA417" t="n">
         <v>10</v>
@@ -91714,31 +91714,31 @@
         </is>
       </c>
       <c r="I419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J419" t="n">
         <v>0</v>
       </c>
       <c r="K419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L419" t="n">
         <v>1</v>
       </c>
       <c r="M419" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N419" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O419" t="inlineStr">
         <is>
-          <t>['-1']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="P419" t="inlineStr">
         <is>
-          <t>['-1', '-1']</t>
+          <t>['81']</t>
         </is>
       </c>
       <c r="Q419" t="n">
@@ -91817,10 +91817,10 @@
         <v>1.53</v>
       </c>
       <c r="AP419" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AQ419" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AQ419" t="n">
-        <v>1.61</v>
       </c>
       <c r="AR419" t="n">
         <v>1.52</v>
@@ -92277,13 +92277,13 @@
         <v>3</v>
       </c>
       <c r="AX421" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AY421" t="n">
         <v>6</v>
       </c>
       <c r="AZ421" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BA421" t="n">
         <v>1</v>
